--- a/public/template/Non-Cash_Template_1.xlsx
+++ b/public/template/Non-Cash_Template_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danny\Documents\GitHub\Teves_Billing_System\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB0704B-9059-4F6F-963F-F48DC1C18354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B51279C-4C48-46EF-8588-F631370EC941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0125C2CC-56FE-4ABB-A7E4-A48064F91EF6}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Template" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Template!$A:$I</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Template!$A:$L</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>San Juan, Madrid Surigao del Sur</t>
   </si>
@@ -46,9 +46,6 @@
     <t>Mobile  : (+63) 948-199-0989 / (+63) 938-406-5237</t>
   </si>
   <si>
-    <t>AMOUNT</t>
-  </si>
-  <si>
     <t>#</t>
   </si>
   <si>
@@ -77,6 +74,18 @@
   </si>
   <si>
     <t>Payment Type</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Reference No.</t>
+  </si>
+  <si>
+    <t>Amount</t>
   </si>
 </sst>
 </file>
@@ -528,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FC95511-3364-44CE-9283-D96B69225C2A}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.77734375" style="6" bestFit="1" customWidth="1"/>
@@ -538,26 +547,32 @@
     <col min="5" max="5" width="16.33203125" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.77734375" style="7" customWidth="1"/>
     <col min="7" max="7" width="16.5546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" style="6" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="2"/>
+    <col min="8" max="8" width="20.88671875" style="7" customWidth="1"/>
+    <col min="9" max="9" width="19.77734375" style="7" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.21875" style="6" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.5" customHeight="1">
+    <row r="1" spans="1:13" ht="31.5" customHeight="1">
       <c r="B1" s="9"/>
       <c r="C1" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="12"/>
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="1"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:10" ht="15" customHeight="1">
+    <row r="2" spans="1:13" ht="15" customHeight="1">
       <c r="B2" s="9"/>
       <c r="C2" s="13" t="s">
         <v>0</v>
@@ -567,8 +582,11 @@
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
       <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
     </row>
-    <row r="3" spans="1:10" ht="17.399999999999999">
+    <row r="3" spans="1:13" ht="17.399999999999999">
       <c r="B3" s="9"/>
       <c r="C3" s="13" t="s">
         <v>1</v>
@@ -578,8 +596,11 @@
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
     </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1">
+    <row r="4" spans="1:13" ht="15" customHeight="1">
       <c r="B4" s="9"/>
       <c r="C4" s="13" t="s">
         <v>1</v>
@@ -589,10 +610,13 @@
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
     </row>
-    <row r="5" spans="1:10" ht="27" customHeight="1">
+    <row r="5" spans="1:13" ht="27" customHeight="1">
       <c r="A5" s="14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
@@ -602,12 +626,15 @@
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
       <c r="I5" s="14"/>
-      <c r="J5" s="3"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1"/>
-    <row r="7" spans="1:10" ht="15.6">
+    <row r="6" spans="1:13" ht="15" customHeight="1"/>
+    <row r="7" spans="1:13" ht="15.6">
       <c r="A7" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="1"/>
@@ -617,10 +644,13 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1">
+    <row r="8" spans="1:13" ht="15" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="9"/>
@@ -628,46 +658,58 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
     </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1"/>
-    <row r="10" spans="1:10" ht="29.4" customHeight="1">
+    <row r="9" spans="1:13" ht="15" customHeight="1"/>
+    <row r="10" spans="1:13" ht="29.4" customHeight="1">
       <c r="A10" s="10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>5</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>6</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="I10" s="11"/>
+      <c r="I10" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="L10" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="K10:L10"/>
     <mergeCell ref="E10:F10"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C2:H2"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="C3:K3"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="C4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="40" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>